--- a/stories/arbres/ATOM-SAN.ECR.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bérénice est dans le salon. Elle regarde un dessin sur la tablette. Les oiseaux chantent dans l'histoire. Papa s'assoit près d'elle. Le canapé est moelleux. Papa dit : fini. L'adulte dit fini. Bérénice écoute. Elle va éteindre. Bérénice éteint l'écran. L'écran devient noir. Elle pose la tablette sur la table. Papa dit : on prend un autre jeu. Bérénice va choisir un jeu. Elle choisit le puzzle des animaux. Les pièces sont lisses. Papa et Bérénice cherchent le lion. Puis l'éléphant. Bérénice dit : l'écran est éteint. Un autre jeu, c'est bien. Parce que l'adulte a dit fini, elle a éteint. Puis elle a un autre jeu. Papa tape doucement dans ses mains. Bérénice rit. Le salon est calme.</t>
+          <t>Bérénice est dans le salon. Elle regarde un dessin sur la tablette. Les oiseaux chantent dans l'histoire. Papa s'assoit près d'elle. Le canapé est moelleux. Fini. L'adulte dit fini. Bérénice écoute. Elle va éteindre. Bérénice éteint l'écran. L'écran devient noir. Elle pose la tablette sur la table. On prend un autre jeu. Bérénice va choisir un jeu. Elle choisit le puzzle des animaux. Les pièces sont lisses. Papa et Bérénice cherchent le lion. Puis l'éléphant. L'écran est éteint. Un autre jeu, c'est bien. Parce que l'adulte a dit fini, elle a éteint. Puis elle a un autre jeu. Papa tape doucement dans ses mains. Bérénice rit. Le salon est calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Bérénice est dans le salon. Elle regarde un dessin sur la tablette. Les oiseaux chantent dans l'histoire. Papa s'assoit près d'elle. Le canapé est moelleux.
+papa|Fini. L'adulte dit fini.
+narrateur|Bérénice écoute. Elle va éteindre. Bérénice éteint l'écran. L'écran devient noir. Elle pose la tablette sur la table.
+papa|On prend un autre jeu.
+narrateur|Bérénice va choisir un jeu. Elle choisit le puzzle des animaux. Les pièces sont lisses. Papa et Bérénice cherchent le lion. Puis l'éléphant.
+enfant-f|L'écran est éteint.
+narrateur|Un autre jeu, c'est bien. Parce que l'adulte a dit fini, elle a éteint. Puis elle a un autre jeu. Papa tape doucement dans ses mains. Bérénice rit. Le salon est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa dit fini. Que fait Bérénice ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Papa a dit fini. Bérénice a éteint. Elle a pris un autre jeu. Le puzzle, c'était bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le lion est en place. Bérénice dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Un autre jeu, c'est bien. Parce que l'adulte a dit fini, elle a éteint. Puis elle a un autre jeu. Papa tape doucement dans ses mains. Bérénice rit. Le salon est calme.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Papa dit fini. Que fait Bérénice ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Papa a dit fini. Bérénice a éteint. Elle a pris un autre jeu. Le puzzle, c'était bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Le lion est en place. Bérénice dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ECR.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bérénice éteint et choisit un puzzle</t>
+          <t>Le puzzle des animaux</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une goutte descend sur la vitre. Papa dit fini. Mila éteint. Elle choisit le puzzle des animaux. Le lion rentre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bérénice est dans le salon. Elle regarde un dessin sur la tablette. Les oiseaux chantent dans l'histoire. Papa s'assoit près d'elle. Le canapé est moelleux. Fini. L'adulte dit fini. Bérénice écoute. Elle va éteindre. Bérénice éteint l'écran. L'écran devient noir. Elle pose la tablette sur la table. On prend un autre jeu. Bérénice va choisir un jeu. Elle choisit le puzzle des animaux. Les pièces sont lisses. Papa et Bérénice cherchent le lion. Puis l'éléphant. L'écran est éteint. Un autre jeu, c'est bien. Parce que l'adulte a dit fini, elle a éteint. Puis elle a un autre jeu. Papa tape doucement dans ses mains. Bérénice rit. Le salon est calme.</t>
+          <t>Une goutte descend sur la vitre. Elle laisse un trait brillant. Le salon sent le coussin chaud. Une couverture jaune dort sur le canapé. Dehors, un oiseau se pose. Son ombre passe sur le tapis. Les chaussettes de Mila sont douces. Mila, viens près de moi. En ce moment, Mila tient la tablette. Un oiseau chante dans l'histoire. Les couleurs bougent tout doucement. Le canapé est moelleux. L'oiseau chante, papa. Oui. Il chante. Papa s'assoit près d'elle. Il pose une main sur la couverture. Fini. L'adulte dit fini. Mila écoute. C'est fini. On va éteindre. Mila va éteindre. Mila éteint l'écran. L'écran devient noir. Elle pose la tablette sur la table. Bravo, Mila. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Mila va vers le tapis. Les pièces du puzzle sont lisses. Elles sentent un peu le carton. Le puzzle des animaux. Très bien. On cherche le lion. Ils cherchent le lion. La crinière est jaune. La pièce rentre. Bravo. Le lion est en place. Et l'éléphant ? Ils cherchent l'éléphant. La pièce est grise et lisse. Elle rentre aussi. L'écran est éteint. Oui. Un autre jeu, c'est bien. Tu as fait du bon travail. Papa tape doucement dans ses mains. Mila rit. La goutte a fini sa descente. Le salon est calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Bérénice est dans le salon. Elle regarde un dessin sur la tablette. Les oiseaux chantent dans l'histoire. Papa s'assoit près d'elle. Le canapé est moelleux.
-papa|Fini. L'adulte dit fini.
-narrateur|Bérénice écoute. Elle va éteindre. Bérénice éteint l'écran. L'écran devient noir. Elle pose la tablette sur la table.
+          <t>narrateur|Une goutte descend sur la vitre.
+narrateur|Elle laisse un trait brillant.
+narrateur|Le salon sent le coussin chaud.
+narrateur|Une couverture jaune dort sur le canapé.
+narrateur|Dehors, un oiseau se pose.
+narrateur|Son ombre passe sur le tapis.
+narrateur|Les chaussettes de Mila sont douces.
+papa|Mila, viens près de moi.
+narrateur|En ce moment, Mila tient la tablette.
+narrateur|Un oiseau chante dans l'histoire.
+narrateur|Les couleurs bougent tout doucement.
+narrateur|Le canapé est moelleux.
+enfant-f|L'oiseau chante, papa.
+papa|Oui.
+papa|Il chante.
+narrateur|Papa s'assoit près d'elle.
+narrateur|Il pose une main sur la couverture.
+papa|Fini.
+narrateur|L'adulte dit fini.
+narrateur|Mila écoute.
+enfant-f|C'est fini.
+papa|On va éteindre.
+narrateur|Mila va éteindre.
+narrateur|Mila éteint l'écran.
+narrateur|L'écran devient noir.
+narrateur|Elle pose la tablette sur la table.
+papa|Bravo, Mila.
+papa|Tu as éteint.
 papa|On prend un autre jeu.
-narrateur|Bérénice va choisir un jeu. Elle choisit le puzzle des animaux. Les pièces sont lisses. Papa et Bérénice cherchent le lion. Puis l'éléphant.
+enfant-f|Un autre jeu.
+papa|Tu choisis ?
+narrateur|Mila va vers le tapis.
+narrateur|Les pièces du puzzle sont lisses.
+narrateur|Elles sentent un peu le carton.
+enfant-f|Le puzzle des animaux.
+papa|Très bien.
+papa|On cherche le lion.
+narrateur|Ils cherchent le lion.
+narrateur|La crinière est jaune.
+narrateur|La pièce rentre.
+papa|Bravo.
+papa|Le lion est en place.
+papa|Et l'éléphant ?
+narrateur|Ils cherchent l'éléphant.
+narrateur|La pièce est grise et lisse.
+narrateur|Elle rentre aussi.
 enfant-f|L'écran est éteint.
-narrateur|Un autre jeu, c'est bien. Parce que l'adulte a dit fini, elle a éteint. Puis elle a un autre jeu. Papa tape doucement dans ses mains. Bérénice rit. Le salon est calme.</t>
+papa|Oui.
+papa|Un autre jeu, c'est bien.
+papa|Tu as fait du bon travail.
+narrateur|Papa tape doucement dans ses mains.
+narrateur|Mila rit.
+narrateur|La goutte a fini sa descente.
+narrateur|Le salon est calme.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>pluie_vitre</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa dit fini. Que fait Bérénice ?</t>
+          <t>Papa dit fini. Que fait Mila ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa dit fini. Que fait Bérénice ?</t>
+          <t>narrateur|Papa dit fini.
+narrateur|Que fait Mila ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Papa a dit fini. Bérénice a éteint. Elle a pris un autre jeu. Le puzzle, c'était bien.</t>
+          <t>Papa a dit fini. L'adulte a dit fini. Mila a éteint. Elle a pris un autre jeu. Tu as éteint l'écran ? Oui, papa. Et après ? Un autre jeu. Bravo. Le puzzle, c'était bien. Mila touche la crinière jaune. La pièce est encore un peu chaude. La vitre brille encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1738,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Papa a dit fini. Bérénice a éteint. Elle a pris un autre jeu. Le puzzle, c'était bien.</t>
+          <t>narrateur|Papa a dit fini.
+narrateur|L'adulte a dit fini.
+narrateur|Mila a éteint.
+narrateur|Elle a pris un autre jeu.
+papa|Tu as éteint l'écran ?
+enfant-f|Oui, papa.
+papa|Et après ?
+enfant-f|Un autre jeu.
+papa|Bravo.
+papa|Le puzzle, c'était bien.
+narrateur|Mila touche la crinière jaune.
+narrateur|La pièce est encore un peu chaude.
+narrateur|La vitre brille encore.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le lion est en place. Bérénice dit merci à papa.</t>
+          <t>Le lion est en place. On range la tablette ? Mila pose la tablette au calme. Tu as fini de ranger ? Oui, papa. Bravo. Merci, papa. Merci, Mila. Tu as éteint. Puis un autre jeu. La couverture jaune reste pliée. Le salon sent encore le coussin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1914,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le lion est en place. Bérénice dit merci à papa.</t>
+          <t>narrateur|Le lion est en place.
+papa|On range la tablette ?
+narrateur|Mila pose la tablette au calme.
+papa|Tu as fini de ranger ?
+enfant-f|Oui, papa.
+papa|Bravo.
+enfant-f|Merci, papa.
+papa|Merci, Mila.
+papa|Tu as éteint.
+papa|Puis un autre jeu.
+narrateur|La couverture jaune reste pliée.
+narrateur|Le salon sent encore le coussin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1953,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le lion veille sur le tapis. L'écran est éteint. Oui. Bravo, Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2093,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le lion veille sur le tapis.
+enfant-f|L'écran est éteint.
+papa|Oui.
+papa|Bravo, Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2157,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte descend sur la vitre. Elle laisse un trait brillant. Le salon sent le coussin chaud. Une couverture jaune dort sur le canapé. Dehors, un oiseau se pose. Son ombre passe sur le tapis. Les chaussettes de Mila sont douces. Mila, viens près de moi. En ce moment, Mila tient la tablette. Un oiseau chante dans l'histoire. Les couleurs bougent tout doucement. Le canapé est moelleux. L'oiseau chante, papa. Oui. Il chante. Papa s'assoit près d'elle. Il pose une main sur la couverture. Fini. L'adulte dit fini. Mila écoute. C'est fini. On va éteindre. Mila va éteindre. Mila éteint l'écran. L'écran devient noir. Elle pose la tablette sur la table. Bravo, Mila. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Mila va vers le tapis. Les pièces du puzzle sont lisses. Elles sentent un peu le carton. Le puzzle des animaux. Très bien. On cherche le lion. Ils cherchent le lion. La crinière est jaune. La pièce rentre. Bravo. Le lion est en place. Et l'éléphant ? Ils cherchent l'éléphant. La pièce est grise et lisse. Elle rentre aussi. L'écran est éteint. Oui. Un autre jeu, c'est bien. Tu as fait du bon travail. Papa tape doucement dans ses mains. Mila rit. La goutte a fini sa descente. Le salon est calme.</t>
+          <t>Une goutte descend sur la vitre. Elle laisse un trait brillant. Le salon sent le coussin chaud. Une couverture jaune dort sur le canapé. Dehors, un oiseau se pose. Son ombre passe sur le tapis. Les chaussettes de Mila sont douces. Un puzzle attend près du tapis. Le carton sent encore le neuf. Mila, viens près de moi. Tu vois l'oiseau dehors ? Oui, papa. Il est gris. En ce moment, Mila tient la tablette. Un oiseau chante dans l'histoire. Les couleurs bougent tout doucement. Le canapé est moelleux. L'oiseau chante, papa. Oui. Il chante. Papa s'assoit près d'elle. Il pose une main sur la couverture. Fini. L'adulte dit fini. Mila écoute. C'est fini. On va éteindre. Mila va éteindre. Mila éteint l'écran. L'écran devient noir. Elle pose la tablette sur la table. Bravo, Mila. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Mila va vers le tapis. Les pièces du puzzle sont lisses. Elles sentent un peu le carton. Le puzzle des animaux. Très bien. On cherche le lion. Ils cherchent le lion. La crinière est jaune. La pièce rentre. Bravo. Le lion est en place. Et l'éléphant ? Ils cherchent l'éléphant. La pièce est grise et lisse. Elle rentre aussi. L'écran est éteint. Oui. Un autre jeu, c'est bien. Papa tape doucement dans ses mains. Mila rit. La goutte a fini sa descente. Le salon est calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bérénice est dans le salon. Elle regarde un dessin sur la tablette. Les oiseaux chantent dans l'histoire. Papa s'assoit près d'elle. Le canapé est moelleux. Papa dit : fini. L'adulte dit fini. Bérénice écoute. Elle va &lt;emphasis level="moderate"&gt;éteindre&lt;/emphasis&gt;. Bérénice éteint l'écran. L'écran devient noir. Elle pose la tablette sur la table. Papa dit : on prend un autre jeu. Bérénice va choisir un jeu. Elle choisit le puzzle des animaux. Les pièces sont lisses. Papa et Bérénice cherchent le lion. Puis l'éléphant. Bérénice dit : l'écran est éteint. Un autre jeu, c'est bien. Parce que l'adulte a dit fini, elle a éteint. Puis elle a un autre jeu. Papa tape doucement dans ses mains. Bérénice rit. Le salon est calme.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une goutte descend sur la vitre. Elle laisse un trait brillant. Le salon sent le coussin chaud. Une couverture jaune dort sur le canapé. Dehors, un oiseau se pose. Son ombre passe sur le tapis. Les chaussettes de Mila sont douces. Un puzzle attend près du tapis. Le carton sent encore le neuf. Mila, viens près de moi. Tu vois l'oiseau dehors ? Oui, papa. Il est gris. En ce moment, Mila tient la tablette. Un oiseau chante dans l'histoire. Les couleurs bougent tout doucement. Le canapé est moelleux. L'oiseau chante, papa. Oui. Il chante. Papa s'assoit près d'elle. Il pose une main sur la couverture. Fini. L'adulte dit fini. Mila écoute. C'est fini. On va éteindre. Mila va éteindre. Mila éteint l'écran. L'écran devient noir. Elle pose la tablette sur la table. Bravo, Mila. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Mila va vers le tapis. Les pièces du puzzle sont lisses. Elles sentent un peu le carton. Le puzzle des animaux. Très bien. On cherche le lion. Ils cherchent le lion. La crinière est jaune. La pièce rentre. Bravo. Le lion est en place. Et l'éléphant ? Ils cherchent l'éléphant. La pièce est grise et lisse. Elle rentre aussi. L'écran est éteint. Oui. Un autre jeu, c'est bien. Papa tape doucement dans ses mains. Mila rit. La goutte a fini sa descente. Le salon est calme.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1331,7 +1331,12 @@
 narrateur|Dehors, un oiseau se pose.
 narrateur|Son ombre passe sur le tapis.
 narrateur|Les chaussettes de Mila sont douces.
+narrateur|Un puzzle attend près du tapis.
+narrateur|Le carton sent encore le neuf.
 papa|Mila, viens près de moi.
+papa|Tu vois l'oiseau dehors ?
+enfant-f|Oui, papa.
+enfant-f|Il est gris.
 narrateur|En ce moment, Mila tient la tablette.
 narrateur|Un oiseau chante dans l'histoire.
 narrateur|Les couleurs bougent tout doucement.
@@ -1373,7 +1378,6 @@
 enfant-f|L'écran est éteint.
 papa|Oui.
 papa|Un autre jeu, c'est bien.
-papa|Tu as fait du bon travail.
 narrateur|Papa tape doucement dans ses mains.
 narrateur|Mila rit.
 narrateur|La goutte a fini sa descente.
@@ -1414,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa dit fini. Que fait Bérénice ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa dit fini. Que fait Mila ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1573,6 @@
 narrateur|Que fait Mila ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1599,7 +1602,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa a dit fini. Bérénice a éteint. Elle a pris un &lt;emphasis level="moderate"&gt;autre&lt;/emphasis&gt; jeu. Le puzzle, c'était bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a dit fini. L'adulte a dit fini. Mila a éteint. Elle a pris un autre jeu. Tu as éteint l'écran ? Oui, papa. Et après ? Un autre jeu. Bravo. Le puzzle, c'était bien. Mila touche la crinière jaune. La pièce est encore un peu chaude. La vitre brille encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1753,7 +1756,6 @@
 narrateur|La vitre brille encore.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,7 +1785,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le lion est en place. Bérénice dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lion est en place. On range la tablette ? Mila pose la tablette au calme. Tu as fini de ranger ? Oui, papa. Bravo. Merci, papa. Merci, Mila. Tu as éteint. Puis un autre jeu. La couverture jaune reste pliée. Le salon sent encore le coussin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1928,7 +1930,6 @@
 narrateur|Le salon sent encore le coussin.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le lion veille sur le tapis. L'écran est éteint. Oui. Bravo, Mila. L'histoire est finie.</t>
+          <t>Le lion veille sur le tapis. L'écran est éteint. Oui. Bravo, Mila.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lion veille sur le tapis. L'écran est éteint. Oui. Bravo, Mila.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2096,11 +2097,9 @@
           <t>narrateur|Le lion veille sur le tapis.
 enfant-f|L'écran est éteint.
 papa|Oui.
-papa|Bravo, Mila.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Mila.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2119,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2163,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, pluie sur la vitre, puzzle des animaux</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bérénice, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
